--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008460309764744066</v>
       </c>
       <c r="C2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>52157476</v>
+        <v>3971705</v>
       </c>
       <c r="L2" t="n">
-        <v>26743810</v>
+        <v>1589000</v>
       </c>
       <c r="M2" t="n">
-        <v>6197404</v>
+        <v>295919</v>
       </c>
       <c r="N2" t="n">
-        <v>277211</v>
+        <v>3777</v>
       </c>
       <c r="O2" t="n">
-        <v>3637737</v>
+        <v>150947</v>
       </c>
       <c r="P2" t="n">
-        <v>1319836</v>
+        <v>24553</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999403357505798</v>
+        <v>0.9998323917388916</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8205649852752686</v>
+        <v>0.7021410465240479</v>
       </c>
       <c r="S2" t="n">
-        <v>0.689433753490448</v>
+        <v>0.5143751502037048</v>
       </c>
       <c r="T2" t="n">
-        <v>0.610323965549469</v>
+        <v>0.3677912950515747</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2426715642213821</v>
+        <v>0.03725991025567055</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6582061648368835</v>
+        <v>0.403259813785553</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7981253862380981</v>
+        <v>0.5772015452384949</v>
       </c>
       <c r="X2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558068513870239</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117310047149658</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579899072647095</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614375710487366</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019421935081482</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026924819488894</v>
       </c>
       <c r="C3" t="n">
-        <v>763</v>
+        <v>188</v>
       </c>
       <c r="D3" t="n">
-        <v>52157476</v>
+        <v>3971705</v>
       </c>
       <c r="E3" t="n">
-        <v>7940694</v>
+        <v>945379</v>
       </c>
       <c r="F3" t="n">
-        <v>264819</v>
+        <v>47659</v>
       </c>
       <c r="G3" t="n">
-        <v>21316</v>
+        <v>3083</v>
       </c>
       <c r="H3" t="n">
-        <v>21071</v>
+        <v>4471</v>
       </c>
       <c r="I3" t="n">
-        <v>1072</v>
+        <v>149</v>
       </c>
       <c r="J3" t="n">
-        <v>120830894</v>
+        <v>10068556</v>
       </c>
       <c r="K3" t="n">
-        <v>125179381</v>
+        <v>9758508</v>
       </c>
       <c r="L3" t="n">
-        <v>145298151</v>
+        <v>11562362</v>
       </c>
       <c r="M3" t="n">
-        <v>181779135</v>
+        <v>14961210</v>
       </c>
       <c r="N3" t="n">
-        <v>195051190</v>
+        <v>16228172</v>
       </c>
       <c r="O3" t="n">
-        <v>188975712</v>
+        <v>15679508</v>
       </c>
       <c r="P3" t="n">
-        <v>194335571</v>
+        <v>16203965</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8634312748908997</v>
+        <v>0.7987124919891357</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6745535731315613</v>
+        <v>0.4738399386405945</v>
       </c>
       <c r="T3" t="n">
-        <v>0.55058753490448</v>
+        <v>0.3127694427967072</v>
       </c>
       <c r="U3" t="n">
-        <v>0.25770503282547</v>
+        <v>0.04185690730810165</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5936951637268066</v>
+        <v>0.2941737174987793</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5682592391967773</v>
+        <v>0.1265292465686798</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2382014</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102565</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82163</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120835440</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133910484</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>153853413</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184139493</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>195552500</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190264326</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>194510227</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957497239112854</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097340106964111</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569492101669312</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660748302936554</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012896418571472</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03198862993387096</v>
       </c>
       <c r="C4" t="n">
-        <v>412</v>
+        <v>180</v>
       </c>
       <c r="D4" t="n">
-        <v>10446526</v>
+        <v>1487275</v>
       </c>
       <c r="E4" t="n">
-        <v>26743810</v>
+        <v>1589000</v>
       </c>
       <c r="F4" t="n">
-        <v>2060652</v>
+        <v>225475</v>
       </c>
       <c r="G4" t="n">
-        <v>126308</v>
+        <v>15768</v>
       </c>
       <c r="H4" t="n">
-        <v>249796</v>
+        <v>34063</v>
       </c>
       <c r="I4" t="n">
-        <v>19175</v>
+        <v>1692</v>
       </c>
       <c r="J4" t="n">
-        <v>4546</v>
+        <v>1064</v>
       </c>
       <c r="K4" t="n">
-        <v>11405408</v>
+        <v>1684858</v>
       </c>
       <c r="L4" t="n">
-        <v>12047170</v>
+        <v>1500185</v>
       </c>
       <c r="M4" t="n">
-        <v>3956882</v>
+        <v>508665</v>
       </c>
       <c r="N4" t="n">
-        <v>865119</v>
+        <v>97592</v>
       </c>
       <c r="O4" t="n">
-        <v>1889007</v>
+        <v>223370</v>
       </c>
       <c r="P4" t="n">
-        <v>333834</v>
+        <v>17985</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999701380729675</v>
+        <v>0.9999161958694458</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8414525389671326</v>
+        <v>0.7473198771476746</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6819124817848206</v>
+        <v>0.4932761788368225</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5789188146591187</v>
+        <v>0.3380561769008636</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2499624788761139</v>
+        <v>0.03942485526204109</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6242884993553162</v>
+        <v>0.3401856422424316</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6638571619987488</v>
+        <v>0.2075591236352921</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2497781</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>999552</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66772</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13821</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2674305</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3491908</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1596524</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>363809</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600393</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566512703895569</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107314348220825</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574692010879517</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610927581787109</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016157984733582</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>823</v>
+        <v>248</v>
       </c>
       <c r="D5" t="n">
-        <v>693288</v>
+        <v>145390</v>
       </c>
       <c r="E5" t="n">
-        <v>3246729</v>
+        <v>397985</v>
       </c>
       <c r="F5" t="n">
-        <v>6197404</v>
+        <v>295919</v>
       </c>
       <c r="G5" t="n">
-        <v>261102</v>
+        <v>24769</v>
       </c>
       <c r="H5" t="n">
-        <v>782396</v>
+        <v>75696</v>
       </c>
       <c r="I5" t="n">
-        <v>74241</v>
+        <v>6118</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8249735</v>
+        <v>1000929</v>
       </c>
       <c r="L5" t="n">
-        <v>12902869</v>
+        <v>1764453</v>
       </c>
       <c r="M5" t="n">
-        <v>5058579</v>
+        <v>650206</v>
       </c>
       <c r="N5" t="n">
-        <v>798480</v>
+        <v>86459</v>
       </c>
       <c r="O5" t="n">
-        <v>2489544</v>
+        <v>362175</v>
       </c>
       <c r="P5" t="n">
-        <v>1002759</v>
+        <v>169497</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999769330024719</v>
+        <v>0.9999352097511292</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9002236723899841</v>
+        <v>0.8363921046257019</v>
       </c>
       <c r="S5" t="n">
-        <v>0.873344898223877</v>
+        <v>0.8011307120323181</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9542343616485596</v>
+        <v>0.9294059872627258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9915549755096436</v>
+        <v>0.9887883067131042</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9777729511260986</v>
+        <v>0.9643308520317078</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9932149648666382</v>
+        <v>0.9885793328285217</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97322</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1034594</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119997</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350660</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2567472</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3578747</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1610177</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364930</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604826</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733909368515015</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641069173812866</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837216734886169</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963006377220154</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99388188123703</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983799457550049</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>850</v>
+        <v>146</v>
       </c>
       <c r="D6" t="n">
-        <v>183057</v>
+        <v>24960</v>
       </c>
       <c r="E6" t="n">
-        <v>236879</v>
+        <v>28152</v>
       </c>
       <c r="F6" t="n">
-        <v>261649</v>
+        <v>24848</v>
       </c>
       <c r="G6" t="n">
-        <v>277211</v>
+        <v>3777</v>
       </c>
       <c r="H6" t="n">
-        <v>105166</v>
+        <v>7775</v>
       </c>
       <c r="I6" t="n">
-        <v>10879</v>
+        <v>578</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78611</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64601</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131879</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84061</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1026</v>
+        <v>255</v>
       </c>
       <c r="D7" t="n">
-        <v>77041</v>
+        <v>24741</v>
       </c>
       <c r="E7" t="n">
-        <v>561572</v>
+        <v>113214</v>
       </c>
       <c r="F7" t="n">
-        <v>1228526</v>
+        <v>173790</v>
       </c>
       <c r="G7" t="n">
-        <v>392912</v>
+        <v>40727</v>
       </c>
       <c r="H7" t="n">
-        <v>3637737</v>
+        <v>150947</v>
       </c>
       <c r="I7" t="n">
-        <v>228467</v>
+        <v>9448</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9726</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358547</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91683</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>672</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>5496</v>
+        <v>2492</v>
       </c>
       <c r="E8" t="n">
-        <v>61296</v>
+        <v>15455</v>
       </c>
       <c r="F8" t="n">
-        <v>141236</v>
+        <v>36893</v>
       </c>
       <c r="G8" t="n">
-        <v>63481</v>
+        <v>13245</v>
       </c>
       <c r="H8" t="n">
-        <v>730578</v>
+        <v>101365</v>
       </c>
       <c r="I8" t="n">
-        <v>1319836</v>
+        <v>24553</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
